--- a/results/Int EDA.xlsx
+++ b/results/Int EDA.xlsx
@@ -554,72 +554,72 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>52.97 ± 9.53</t>
+          <t>64.56 ± 5.37</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.66 ± 9.52</t>
+          <t>64.56 ± 5.52</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>51.90 ± 9.63</t>
+          <t>64.13 ± 5.61</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>53.59 ± 12.57</t>
+          <t>70.22 ± 5.62</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>57.11 ± 11.20</t>
+          <t>72.96 ± 7.02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.89 ± 18.91</t>
+          <t>29.01 ± 10.91</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>57.10 ± 11.21</t>
+          <t>72.92 ± 7.03</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>47.66 ± 10.10</t>
+          <t>35.41 ± 4.34</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>17.59 ± 14.98</t>
+          <t>31.73 ± 15.30</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>10.88 ± 12.97</t>
+          <t>23.03 ± 15.00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -662,72 +662,72 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>49.93 ± 4.29</t>
+          <t>57.84 ± 4.09</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.96 ± 4.36</t>
+          <t>58.01 ± 4.11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>49.85 ± 4.39</t>
+          <t>57.73 ± 4.16</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>49.62 ± 6.28</t>
+          <t>60.56 ± 5.90</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>52.65 ± 6.39</t>
+          <t>63.80 ± 5.86</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.14 ± 8.56</t>
+          <t>15.64 ± 8.15</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>54.50 ± 7.03</t>
+          <t>67.52 ± 6.01</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.07 ± 4.46</t>
+          <t>41.75 ± 4.07</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12.77 ± 8.70</t>
+          <t>19.34 ± 13.13</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>6.17 ± 7.56</t>
+          <t>9.77 ± 10.57</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -770,42 +770,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>48.87 ± 2.52</t>
+          <t>57.20 ± 5.96</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.88 ± 2.36</t>
+          <t>57.50 ± 6.24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>48.60 ± 2.55</t>
+          <t>57.21 ± 6.20</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48.34 ± 2.68</t>
+          <t>58.72 ± 5.90</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50.46 ± 2.11</t>
+          <t>59.39 ± 4.45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-2.28 ± 5.02</t>
+          <t>14.46 ± 11.91</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>59.94 ± 3.23</t>
+          <t>70.65 ± 5.44</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>51.37 ± 2.50</t>
+          <t>42.80 ± 5.26</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -820,22 +820,22 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -878,72 +878,72 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>46.61 ± 3.96</t>
+          <t>58.87 ± 5.06</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>46.67 ± 3.78</t>
+          <t>59.45 ± 5.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>46.24 ± 3.86</t>
+          <t>58.83 ± 5.11</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>46.34 ± 4.12</t>
+          <t>63.93 ± 6.92</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>51.44 ± 5.35</t>
+          <t>68.11 ± 6.31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-6.80 ± 7.88</t>
+          <t>17.88 ± 10.15</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>51.55 ± 5.25</t>
+          <t>68.16 ± 6.35</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>53.54 ± 3.15</t>
+          <t>40.03 ± 5.64</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>11.63 ± 4.99</t>
+          <t>25.70 ± 11.49</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>7.80 ± 4.22</t>
+          <t>15.77 ± 6.47</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -986,72 +986,72 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>52.97 ± 9.53</t>
+          <t>64.56 ± 5.37</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.66 ± 9.52</t>
+          <t>64.56 ± 5.52</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>51.90 ± 9.63</t>
+          <t>64.13 ± 5.61</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>53.59 ± 12.57</t>
+          <t>70.22 ± 5.62</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>57.11 ± 11.20</t>
+          <t>72.96 ± 7.02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.89 ± 18.91</t>
+          <t>29.01 ± 10.91</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>57.10 ± 11.21</t>
+          <t>72.92 ± 7.03</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>47.66 ± 10.10</t>
+          <t>35.41 ± 4.34</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>17.59 ± 14.98</t>
+          <t>31.73 ± 15.30</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>10.88 ± 12.97</t>
+          <t>23.03 ± 15.00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1094,72 +1094,72 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>49.93 ± 4.29</t>
+          <t>57.84 ± 4.09</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.96 ± 4.36</t>
+          <t>58.01 ± 4.11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>49.85 ± 4.39</t>
+          <t>57.73 ± 4.16</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>49.65 ± 6.27</t>
+          <t>60.62 ± 5.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>52.73 ± 6.33</t>
+          <t>63.80 ± 5.86</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.14 ± 8.56</t>
+          <t>15.64 ± 8.15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>54.56 ± 6.99</t>
+          <t>67.53 ± 6.00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.07 ± 4.46</t>
+          <t>41.75 ± 4.07</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12.77 ± 8.70</t>
+          <t>19.34 ± 13.13</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>7.13 ± 7.32</t>
+          <t>9.77 ± 10.57</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1202,42 +1202,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>48.87 ± 2.52</t>
+          <t>57.20 ± 5.96</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.88 ± 2.36</t>
+          <t>57.50 ± 6.24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>48.60 ± 2.55</t>
+          <t>57.21 ± 6.20</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>48.34 ± 2.68</t>
+          <t>58.72 ± 5.90</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50.46 ± 2.11</t>
+          <t>59.39 ± 4.45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-2.28 ± 5.02</t>
+          <t>14.46 ± 11.91</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>59.94 ± 3.23</t>
+          <t>70.65 ± 5.44</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>51.37 ± 2.50</t>
+          <t>42.80 ± 5.26</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1252,22 +1252,22 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1310,72 +1310,72 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.56 ± 4.04</t>
+          <t>59.07 ± 4.54</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>46.61 ± 3.87</t>
+          <t>59.67 ± 4.74</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>46.18 ± 3.93</t>
+          <t>59.00 ± 4.61</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>46.25 ± 4.33</t>
+          <t>63.92 ± 7.03</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>51.25 ± 5.34</t>
+          <t>68.35 ± 6.35</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-6.92 ± 8.05</t>
+          <t>18.29 ± 9.10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>51.36 ± 5.23</t>
+          <t>68.37 ± 6.36</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>53.66 ± 3.34</t>
+          <t>39.74 ± 5.62</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>11.41 ± 4.97</t>
+          <t>25.45 ± 11.76</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>7.73 ± 4.21</t>
+          <t>15.90 ± 7.45</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1418,72 +1418,72 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>52.97 ± 9.53</t>
+          <t>64.56 ± 5.37</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52.66 ± 9.52</t>
+          <t>64.56 ± 5.52</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>51.90 ± 9.63</t>
+          <t>64.13 ± 5.61</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>53.59 ± 12.57</t>
+          <t>70.22 ± 5.62</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>57.11 ± 11.20</t>
+          <t>72.96 ± 7.02</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.89 ± 18.91</t>
+          <t>29.01 ± 10.91</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>57.10 ± 11.21</t>
+          <t>72.92 ± 7.03</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>47.66 ± 10.10</t>
+          <t>35.41 ± 4.34</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>17.59 ± 14.98</t>
+          <t>31.73 ± 15.30</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10.88 ± 12.97</t>
+          <t>23.03 ± 15.00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1526,72 +1526,72 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>49.80 ± 4.09</t>
+          <t>57.84 ± 4.09</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.84 ± 4.17</t>
+          <t>58.01 ± 4.11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>49.73 ± 4.21</t>
+          <t>57.73 ± 4.16</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>49.67 ± 6.10</t>
+          <t>60.62 ± 5.85</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>52.72 ± 6.21</t>
+          <t>63.89 ± 5.81</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.38 ± 8.17</t>
+          <t>15.64 ± 8.15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>54.56 ± 6.86</t>
+          <t>67.58 ± 5.99</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.13 ± 4.25</t>
+          <t>41.75 ± 4.07</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12.77 ± 8.70</t>
+          <t>22.20 ± 11.66</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>6.59 ± 7.42</t>
+          <t>9.80 ± 10.64</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1634,42 +1634,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>48.87 ± 2.52</t>
+          <t>57.20 ± 5.96</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.88 ± 2.36</t>
+          <t>57.50 ± 6.24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>48.60 ± 2.55</t>
+          <t>57.21 ± 6.20</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>48.34 ± 2.68</t>
+          <t>58.72 ± 5.90</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50.46 ± 2.11</t>
+          <t>59.39 ± 4.45</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.28 ± 5.02</t>
+          <t>14.46 ± 11.91</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>59.94 ± 3.23</t>
+          <t>70.65 ± 5.44</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>51.37 ± 2.50</t>
+          <t>42.80 ± 5.26</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1684,22 +1684,22 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1742,72 +1742,72 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>46.69 ± 3.90</t>
+          <t>58.83 ± 5.24</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>46.75 ± 3.73</t>
+          <t>59.43 ± 5.40</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>46.33 ± 3.81</t>
+          <t>58.74 ± 5.31</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>46.27 ± 4.17</t>
+          <t>63.95 ± 7.32</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>51.27 ± 5.17</t>
+          <t>68.60 ± 6.39</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-6.65 ± 7.77</t>
+          <t>17.81 ± 10.49</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>51.39 ± 5.05</t>
+          <t>68.63 ± 6.39</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>53.59 ± 3.35</t>
+          <t>39.84 ± 5.95</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>11.21 ± 4.96</t>
+          <t>26.06 ± 11.63</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7.47 ± 4.01</t>
+          <t>16.68 ± 7.01</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1850,72 +1850,72 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>52.97 ± 9.53</t>
+          <t>64.56 ± 5.37</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>52.66 ± 9.52</t>
+          <t>64.56 ± 5.52</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>51.90 ± 9.63</t>
+          <t>64.13 ± 5.61</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>53.59 ± 12.57</t>
+          <t>70.22 ± 5.62</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>57.11 ± 11.20</t>
+          <t>72.96 ± 7.02</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5.89 ± 18.91</t>
+          <t>29.01 ± 10.91</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>57.10 ± 11.21</t>
+          <t>72.92 ± 7.03</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>47.66 ± 10.10</t>
+          <t>35.41 ± 4.34</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>17.59 ± 14.98</t>
+          <t>31.73 ± 15.30</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>10.88 ± 12.97</t>
+          <t>23.03 ± 15.00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1958,72 +1958,72 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>50.11 ± 4.10</t>
+          <t>57.84 ± 4.09</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>50.15 ± 4.13</t>
+          <t>58.01 ± 4.11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>50.06 ± 4.16</t>
+          <t>57.73 ± 4.16</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>49.86 ± 6.10</t>
+          <t>60.83 ± 5.82</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>52.82 ± 6.28</t>
+          <t>63.88 ± 5.86</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.21 ± 8.20</t>
+          <t>15.64 ± 8.15</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>54.67 ± 6.92</t>
+          <t>67.61 ± 5.98</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>49.87 ± 4.26</t>
+          <t>41.75 ± 4.07</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>12.77 ± 8.70</t>
+          <t>19.38 ± 13.18</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>6.97 ± 7.17</t>
+          <t>9.77 ± 10.57</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2066,42 +2066,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>48.87 ± 2.52</t>
+          <t>57.20 ± 5.96</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>48.88 ± 2.36</t>
+          <t>57.50 ± 6.24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>48.60 ± 2.55</t>
+          <t>57.21 ± 6.20</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>48.34 ± 2.68</t>
+          <t>58.72 ± 5.90</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50.46 ± 2.11</t>
+          <t>59.39 ± 4.45</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-2.28 ± 5.02</t>
+          <t>14.46 ± 11.91</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>59.94 ± 3.23</t>
+          <t>70.65 ± 5.44</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>51.37 ± 2.50</t>
+          <t>42.80 ± 5.26</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2116,22 +2116,22 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2174,72 +2174,72 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>46.62 ± 4.10</t>
+          <t>59.15 ± 5.02</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>46.67 ± 3.90</t>
+          <t>59.73 ± 5.24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>46.23 ± 3.96</t>
+          <t>59.11 ± 5.14</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>46.13 ± 4.33</t>
+          <t>64.13 ± 7.16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>51.18 ± 5.28</t>
+          <t>68.63 ± 6.39</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-6.79 ± 8.15</t>
+          <t>18.45 ± 10.07</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>51.24 ± 5.23</t>
+          <t>68.67 ± 6.40</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>53.73 ± 3.38</t>
+          <t>39.99 ± 5.67</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>11.35 ± 4.77</t>
+          <t>26.02 ± 10.88</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>7.78 ± 4.30</t>
+          <t>15.99 ± 6.85</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2282,72 +2282,72 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>52.97 ± 9.53</t>
+          <t>64.56 ± 5.37</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>52.66 ± 9.52</t>
+          <t>64.56 ± 5.52</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>51.90 ± 9.63</t>
+          <t>64.13 ± 5.61</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>53.59 ± 12.57</t>
+          <t>70.22 ± 5.62</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>57.11 ± 11.20</t>
+          <t>72.96 ± 7.02</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>5.89 ± 18.91</t>
+          <t>29.01 ± 10.91</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>57.10 ± 11.21</t>
+          <t>72.92 ± 7.03</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>47.66 ± 10.10</t>
+          <t>35.41 ± 4.34</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17.59 ± 14.98</t>
+          <t>31.73 ± 15.30</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>10.88 ± 12.97</t>
+          <t>23.03 ± 15.00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2390,72 +2390,72 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>49.85 ± 4.19</t>
+          <t>57.84 ± 4.09</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>49.88 ± 4.25</t>
+          <t>58.01 ± 4.11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>49.76 ± 4.28</t>
+          <t>57.73 ± 4.16</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>49.68 ± 6.19</t>
+          <t>60.55 ± 5.89</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>52.64 ± 6.29</t>
+          <t>63.79 ± 5.86</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-0.30 ± 8.36</t>
+          <t>15.64 ± 8.15</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>54.49 ± 6.90</t>
+          <t>67.51 ± 6.00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>50.02 ± 4.38</t>
+          <t>41.75 ± 4.07</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>12.61 ± 8.53</t>
+          <t>19.34 ± 13.13</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>6.01 ± 7.39</t>
+          <t>9.77 ± 10.57</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2498,42 +2498,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>48.87 ± 2.52</t>
+          <t>57.20 ± 5.96</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>48.88 ± 2.36</t>
+          <t>57.50 ± 6.24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>48.60 ± 2.55</t>
+          <t>57.21 ± 6.20</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>48.34 ± 2.68</t>
+          <t>58.72 ± 5.90</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50.46 ± 2.11</t>
+          <t>59.39 ± 4.45</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-2.28 ± 5.02</t>
+          <t>14.46 ± 11.91</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>59.94 ± 3.23</t>
+          <t>70.65 ± 5.44</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>51.37 ± 2.50</t>
+          <t>42.80 ± 5.26</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2548,22 +2548,22 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2606,72 +2606,72 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>46.62 ± 4.41</t>
+          <t>58.90 ± 5.08</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>46.66 ± 4.23</t>
+          <t>59.49 ± 5.27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>46.24 ± 4.28</t>
+          <t>58.81 ± 5.20</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>46.34 ± 4.42</t>
+          <t>63.96 ± 7.06</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>51.34 ± 5.49</t>
+          <t>68.02 ± 6.14</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-6.79 ± 8.78</t>
+          <t>17.95 ± 10.17</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>51.45 ± 5.39</t>
+          <t>68.08 ± 6.19</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>53.44 ± 3.42</t>
+          <t>40.01 ± 5.82</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>11.47 ± 4.95</t>
+          <t>26.34 ± 12.10</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>7.95 ± 4.19</t>
+          <t>15.53 ± 6.40</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>51.33 ± 0.01</t>
+          <t>54.09 ± 0.01</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>48.67 ± 0.01</t>
+          <t>45.91 ± 0.01</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>51.31 ± 0.00</t>
+          <t>54.06 ± 0.00</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>48.69 ± 0.00</t>
+          <t>45.94 ± 0.00</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2714,72 +2714,72 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>52.85 ± 8.36</t>
+          <t>64.81 ± 8.68</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>52.90 ± 8.28</t>
+          <t>64.81 ± 8.61</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>51.49 ± 8.54</t>
+          <t>64.34 ± 9.05</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>52.97 ± 9.47</t>
+          <t>69.91 ± 8.95</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>54.78 ± 6.81</t>
+          <t>73.23 ± 9.15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>5.68 ± 16.68</t>
+          <t>29.48 ± 17.20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>54.76 ± 6.81</t>
+          <t>73.21 ± 9.16</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>47.35 ± 7.96</t>
+          <t>34.69 ± 7.96</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>14.09 ± 8.83</t>
+          <t>34.91 ± 15.85</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>6.18 ± 5.75</t>
+          <t>25.61 ± 15.20</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>50.59 ± 0.02</t>
+          <t>53.34 ± 0.02</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>49.41 ± 0.02</t>
+          <t>46.66 ± 0.02</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>50.58 ± 0.00</t>
+          <t>53.32 ± 0.00</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>49.42 ± 0.00</t>
+          <t>46.68 ± 0.00</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2822,72 +2822,72 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>49.94 ± 3.32</t>
+          <t>58.66 ± 5.41</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>50.03 ± 3.38</t>
+          <t>58.83 ± 5.35</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>49.95 ± 3.36</t>
+          <t>58.59 ± 5.48</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>49.55 ± 3.98</t>
+          <t>61.59 ± 8.14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>51.24 ± 3.49</t>
+          <t>63.90 ± 8.83</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-0.12 ± 6.62</t>
+          <t>17.29 ± 10.76</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>53.03 ± 4.36</t>
+          <t>67.79 ± 8.39</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>50.02 ± 3.27</t>
+          <t>41.32 ± 5.90</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>11.21 ± 4.66</t>
+          <t>27.40 ± 15.73</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4.70 ± 3.93</t>
+          <t>13.75 ± 15.08</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>50.59 ± 0.02</t>
+          <t>53.34 ± 0.02</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>49.41 ± 0.02</t>
+          <t>46.66 ± 0.02</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>50.58 ± 0.00</t>
+          <t>53.32 ± 0.00</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>49.42 ± 0.00</t>
+          <t>46.68 ± 0.00</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2930,42 +2930,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>48.29 ± 4.65</t>
+          <t>56.65 ± 4.59</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>48.27 ± 4.60</t>
+          <t>57.12 ± 4.90</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>48.14 ± 4.67</t>
+          <t>56.82 ± 4.68</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>48.15 ± 5.52</t>
+          <t>58.26 ± 4.99</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>49.79 ± 3.76</t>
+          <t>58.69 ± 4.72</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-3.43 ± 9.30</t>
+          <t>13.41 ± 9.31</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>59.19 ± 4.68</t>
+          <t>70.21 ± 4.71</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>51.55 ± 5.01</t>
+          <t>43.33 ± 4.52</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2980,22 +2980,22 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>50.59 ± 0.02</t>
+          <t>53.34 ± 0.02</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>49.41 ± 0.02</t>
+          <t>46.66 ± 0.02</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>50.58 ± 0.00</t>
+          <t>53.32 ± 0.00</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>49.42 ± 0.00</t>
+          <t>46.68 ± 0.00</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3038,72 +3038,72 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>46.78 ± 7.54</t>
+          <t>59.51 ± 6.58</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>46.79 ± 7.45</t>
+          <t>60.15 ± 6.73</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>46.66 ± 7.49</t>
+          <t>59.64 ± 6.73</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>46.38 ± 9.67</t>
+          <t>64.47 ± 8.83</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>48.95 ± 6.70</t>
+          <t>67.67 ± 8.51</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-6.47 ± 15.06</t>
+          <t>19.22 ± 13.32</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>49.08 ± 6.61</t>
+          <t>67.68 ± 8.50</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>53.35 ± 7.85</t>
+          <t>39.54 ± 6.98</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9.42 ± 5.28</t>
+          <t>27.22 ± 12.92</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>5.24 ± 3.23</t>
+          <t>17.52 ± 9.25</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>50.59 ± 0.02</t>
+          <t>53.34 ± 0.02</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>49.41 ± 0.02</t>
+          <t>46.66 ± 0.02</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>50.58 ± 0.00</t>
+          <t>53.32 ± 0.00</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>49.42 ± 0.00</t>
+          <t>46.68 ± 0.00</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3146,72 +3146,72 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>51.77 ± 8.35</t>
+          <t>65.01 ± 6.66</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>51.78 ± 8.35</t>
+          <t>64.99 ± 6.40</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>50.60 ± 8.62</t>
+          <t>64.86 ± 6.43</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>51.92 ± 11.20</t>
+          <t>69.52 ± 8.66</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>53.88 ± 10.71</t>
+          <t>71.01 ± 9.86</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3.53 ± 16.53</t>
+          <t>29.83 ± 13.09</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>53.86 ± 10.72</t>
+          <t>70.98 ± 9.90</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>48.06 ± 8.17</t>
+          <t>35.35 ± 5.99</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>14.57 ± 13.98</t>
+          <t>33.24 ± 14.24</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>9.64 ± 11.65</t>
+          <t>21.12 ± 14.94</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>49.81 ± 0.02</t>
+          <t>52.80 ± 0.02</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>50.19 ± 0.02</t>
+          <t>47.20 ± 0.02</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>49.82 ± 0.00</t>
+          <t>52.81 ± 0.00</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>50.18 ± 0.00</t>
+          <t>47.19 ± 0.00</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3254,72 +3254,72 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>49.74 ± 4.57</t>
+          <t>58.53 ± 5.43</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>49.81 ± 4.60</t>
+          <t>58.57 ± 5.39</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>49.71 ± 4.62</t>
+          <t>58.56 ± 5.43</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>49.18 ± 6.65</t>
+          <t>61.32 ± 8.30</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>50.88 ± 6.10</t>
+          <t>63.59 ± 8.51</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-0.52 ± 9.13</t>
+          <t>16.99 ± 10.80</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>52.50 ± 6.95</t>
+          <t>67.43 ± 7.70</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>50.44 ± 4.60</t>
+          <t>41.72 ± 5.58</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>12.92 ± 8.15</t>
+          <t>24.54 ± 14.15</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>6.60 ± 6.18</t>
+          <t>13.16 ± 12.09</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>49.81 ± 0.02</t>
+          <t>52.80 ± 0.02</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>50.19 ± 0.02</t>
+          <t>47.20 ± 0.02</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>49.82 ± 0.00</t>
+          <t>52.81 ± 0.00</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>50.18 ± 0.00</t>
+          <t>47.19 ± 0.00</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3362,42 +3362,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.96 ± 4.63</t>
+          <t>59.19 ± 4.68</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>48.94 ± 4.64</t>
+          <t>59.49 ± 4.76</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>48.73 ± 4.64</t>
+          <t>59.40 ± 4.73</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>48.74 ± 5.33</t>
+          <t>60.11 ± 4.73</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>49.63 ± 4.45</t>
+          <t>59.28 ± 4.48</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-2.08 ± 9.23</t>
+          <t>18.43 ± 9.44</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>59.01 ± 4.70</t>
+          <t>70.63 ± 4.34</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>51.53 ± 4.96</t>
+          <t>41.22 ± 4.61</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3412,22 +3412,22 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>49.81 ± 0.02</t>
+          <t>52.80 ± 0.02</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>50.19 ± 0.02</t>
+          <t>47.20 ± 0.02</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>49.82 ± 0.00</t>
+          <t>52.81 ± 0.00</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>50.18 ± 0.00</t>
+          <t>47.19 ± 0.00</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3470,72 +3470,72 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>47.11 ± 6.36</t>
+          <t>60.62 ± 5.12</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>47.10 ± 6.29</t>
+          <t>60.95 ± 5.17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>46.71 ± 6.34</t>
+          <t>60.78 ± 5.21</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>46.99 ± 8.56</t>
+          <t>64.96 ± 7.07</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>49.18 ± 9.35</t>
+          <t>66.36 ± 9.10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-5.79 ± 12.66</t>
+          <t>21.30 ± 10.26</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>49.22 ± 9.34</t>
+          <t>66.37 ± 9.10</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>52.78 ± 6.43</t>
+          <t>39.05 ± 5.22</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>11.29 ± 10.50</t>
+          <t>23.93 ± 11.10</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>7.01 ± 8.23</t>
+          <t>14.12 ± 10.95</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>49.81 ± 0.02</t>
+          <t>52.80 ± 0.02</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>50.19 ± 0.02</t>
+          <t>47.20 ± 0.02</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>49.82 ± 0.00</t>
+          <t>52.81 ± 0.00</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>50.18 ± 0.00</t>
+          <t>47.19 ± 0.00</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3578,72 +3578,72 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>53.62 ± 6.04</t>
+          <t>64.61 ± 5.16</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>54.15 ± 6.38</t>
+          <t>64.47 ± 5.04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>52.55 ± 6.40</t>
+          <t>64.42 ± 5.04</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>53.94 ± 7.90</t>
+          <t>68.74 ± 5.55</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>55.74 ± 5.47</t>
+          <t>69.31 ± 7.29</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>7.36 ± 12.14</t>
+          <t>29.06 ± 10.18</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>55.72 ± 5.47</t>
+          <t>69.28 ± 7.29</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>47.48 ± 6.45</t>
+          <t>35.21 ± 4.99</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>18.67 ± 7.38</t>
+          <t>31.03 ± 14.41</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>11.77 ± 8.03</t>
+          <t>19.41 ± 11.03</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>48.65 ± 0.02</t>
+          <t>51.52 ± 0.02</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>51.35 ± 0.02</t>
+          <t>48.48 ± 0.02</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>48.66 ± 0.00</t>
+          <t>51.53 ± 0.00</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>51.34 ± 0.00</t>
+          <t>48.47 ± 0.00</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3686,72 +3686,72 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>50.32 ± 3.50</t>
+          <t>58.24 ± 4.68</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>50.44 ± 3.61</t>
+          <t>58.20 ± 4.64</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>50.32 ± 3.58</t>
+          <t>58.15 ± 4.62</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>50.12 ± 4.44</t>
+          <t>60.55 ± 6.29</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50.45 ± 3.84</t>
+          <t>61.16 ± 6.92</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.65 ± 6.99</t>
+          <t>16.41 ± 9.29</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>52.71 ± 3.83</t>
+          <t>65.14 ± 6.32</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>50.02 ± 3.37</t>
+          <t>41.75 ± 4.59</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>13.03 ± 5.38</t>
+          <t>22.55 ± 13.25</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>6.99 ± 4.00</t>
+          <t>11.96 ± 10.69</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>48.65 ± 0.02</t>
+          <t>51.52 ± 0.02</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>51.35 ± 0.02</t>
+          <t>48.48 ± 0.02</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>48.66 ± 0.00</t>
+          <t>51.53 ± 0.00</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>51.34 ± 0.00</t>
+          <t>48.47 ± 0.00</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3794,42 +3794,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>47.05 ± 4.32</t>
+          <t>56.44 ± 4.27</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>47.09 ± 4.31</t>
+          <t>56.53 ± 4.32</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>47.05 ± 4.30</t>
+          <t>56.31 ± 4.35</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>47.35 ± 4.81</t>
+          <t>57.96 ± 5.36</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>47.62 ± 4.31</t>
+          <t>56.59 ± 3.54</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-5.87 ± 8.61</t>
+          <t>12.87 ± 8.59</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>57.01 ± 4.56</t>
+          <t>68.09 ± 3.84</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>52.78 ± 4.44</t>
+          <t>42.48 ± 5.19</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3844,22 +3844,22 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>48.65 ± 0.02</t>
+          <t>51.52 ± 0.02</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>51.35 ± 0.02</t>
+          <t>48.48 ± 0.02</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>48.66 ± 0.00</t>
+          <t>51.53 ± 0.00</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>51.34 ± 0.00</t>
+          <t>48.47 ± 0.00</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3902,72 +3902,72 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>46.95 ± 6.23</t>
+          <t>58.48 ± 5.97</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>46.95 ± 6.22</t>
+          <t>58.54 ± 5.96</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>46.89 ± 6.16</t>
+          <t>58.18 ± 6.10</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>46.81 ± 8.41</t>
+          <t>62.30 ± 8.45</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>49.13 ± 7.10</t>
+          <t>63.61 ± 7.11</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-6.05 ± 12.40</t>
+          <t>16.95 ± 11.97</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>49.19 ± 7.06</t>
+          <t>63.64 ± 7.08</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>53.04 ± 6.41</t>
+          <t>41.70 ± 5.89</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>12.44 ± 4.46</t>
+          <t>23.21 ± 10.93</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>7.60 ± 3.28</t>
+          <t>13.86 ± 8.45</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>48.65 ± 0.02</t>
+          <t>51.52 ± 0.02</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>51.35 ± 0.02</t>
+          <t>48.48 ± 0.02</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>48.66 ± 0.00</t>
+          <t>51.53 ± 0.00</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>51.34 ± 0.00</t>
+          <t>48.47 ± 0.00</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4010,72 +4010,72 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>54.68 ± 5.71</t>
+          <t>66.10 ± 9.32</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>55.81 ± 5.65</t>
+          <t>65.86 ± 9.40</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>53.39 ± 6.22</t>
+          <t>65.41 ± 9.75</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>54.68 ± 9.25</t>
+          <t>70.70 ± 10.80</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>54.43 ± 9.84</t>
+          <t>70.77 ± 11.05</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>9.53 ± 11.61</t>
+          <t>32.05 ± 18.65</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>54.42 ± 9.84</t>
+          <t>70.75 ± 11.06</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>46.49 ± 6.14</t>
+          <t>34.51 ± 9.48</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>19.05 ± 13.10</t>
+          <t>35.32 ± 17.28</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>10.72 ± 10.66</t>
+          <t>23.73 ± 16.30</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>47.52 ± 0.01</t>
+          <t>50.38 ± 0.02</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>52.48 ± 0.01</t>
+          <t>49.62 ± 0.02</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>47.50 ± 0.00</t>
+          <t>50.38 ± 0.00</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>52.50 ± 0.00</t>
+          <t>49.62 ± 0.00</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4118,72 +4118,72 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>49.90 ± 3.53</t>
+          <t>59.09 ± 6.18</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>50.27 ± 3.45</t>
+          <t>58.93 ± 6.15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>50.00 ± 3.52</t>
+          <t>58.63 ± 6.27</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>48.85 ± 5.06</t>
+          <t>61.02 ± 7.70</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>48.22 ± 4.40</t>
+          <t>60.72 ± 8.05</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-0.20 ± 7.06</t>
+          <t>18.10 ± 12.33</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>50.13 ± 5.02</t>
+          <t>64.61 ± 8.06</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>50.65 ± 3.70</t>
+          <t>41.36 ± 6.41</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>11.80 ± 4.49</t>
+          <t>21.13 ± 14.82</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>6.78 ± 4.79</t>
+          <t>11.35 ± 12.76</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>47.52 ± 0.01</t>
+          <t>50.38 ± 0.02</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>52.48 ± 0.01</t>
+          <t>49.62 ± 0.02</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>47.50 ± 0.00</t>
+          <t>50.38 ± 0.00</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>52.50 ± 0.00</t>
+          <t>49.62 ± 0.00</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4226,42 +4226,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>48.99 ± 4.56</t>
+          <t>56.20 ± 6.61</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>49.10 ± 4.47</t>
+          <t>56.10 ± 6.53</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>48.99 ± 4.44</t>
+          <t>55.93 ± 6.49</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>48.68 ± 4.85</t>
+          <t>57.67 ± 6.79</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>47.31 ± 3.67</t>
+          <t>55.75 ± 5.30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-2.03 ± 9.11</t>
+          <t>12.33 ± 13.15</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>56.72 ± 4.60</t>
+          <t>67.46 ± 5.02</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>51.38 ± 4.60</t>
+          <t>43.57 ± 6.27</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>47.52 ± 0.01</t>
+          <t>50.38 ± 0.02</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>52.48 ± 0.01</t>
+          <t>49.62 ± 0.02</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>47.50 ± 0.00</t>
+          <t>50.38 ± 0.00</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>52.50 ± 0.00</t>
+          <t>49.62 ± 0.00</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4334,72 +4334,72 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>47.49 ± 5.88</t>
+          <t>60.29 ± 8.75</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>47.62 ± 5.80</t>
+          <t>60.22 ± 8.69</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>47.54 ± 5.74</t>
+          <t>60.01 ± 8.89</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>47.31 ± 7.57</t>
+          <t>64.00 ± 10.83</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>47.52 ± 7.41</t>
+          <t>65.34 ± 10.74</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-5.01 ± 11.74</t>
+          <t>20.50 ± 17.43</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>47.56 ± 7.39</t>
+          <t>65.34 ± 10.71</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>52.45 ± 5.86</t>
+          <t>39.03 ± 8.59</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>11.64 ± 7.08</t>
+          <t>26.87 ± 14.35</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6.42 ± 4.29</t>
+          <t>18.24 ± 11.70</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>47.52 ± 0.01</t>
+          <t>50.38 ± 0.02</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>52.48 ± 0.01</t>
+          <t>49.62 ± 0.02</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>47.50 ± 0.00</t>
+          <t>50.38 ± 0.00</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>52.50 ± 0.00</t>
+          <t>49.62 ± 0.00</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4442,72 +4442,72 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>53.93 ± 7.24</t>
+          <t>65.16 ± 7.61</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>56.87 ± 6.94</t>
+          <t>65.85 ± 7.03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>52.85 ± 8.16</t>
+          <t>64.81 ± 7.67</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>54.14 ± 10.15</t>
+          <t>69.03 ± 9.51</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>52.12 ± 11.36</t>
+          <t>67.44 ± 12.45</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>8.13 ± 15.18</t>
+          <t>30.47 ± 15.01</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>52.11 ± 11.36</t>
+          <t>67.41 ± 12.47</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>46.55 ± 7.92</t>
+          <t>35.27 ± 6.47</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>18.56 ± 14.48</t>
+          <t>34.52 ± 19.36</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>12.12 ± 9.96</t>
+          <t>25.17 ± 17.78</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>44.87 ± 0.02</t>
+          <t>47.86 ± 0.03</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>55.13 ± 0.02</t>
+          <t>52.14 ± 0.03</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>44.90 ± 0.00</t>
+          <t>47.89 ± 0.00</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>55.10 ± 0.00</t>
+          <t>52.11 ± 0.00</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4550,72 +4550,72 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>49.13 ± 5.01</t>
+          <t>58.94 ± 6.91</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>50.50 ± 4.67</t>
+          <t>59.45 ± 6.44</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>49.79 ± 4.92</t>
+          <t>58.79 ± 6.89</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>47.55 ± 7.32</t>
+          <t>60.38 ± 8.65</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>46.33 ± 6.86</t>
+          <t>57.96 ± 10.27</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-1.83 ± 10.14</t>
+          <t>17.87 ± 13.69</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>47.42 ± 7.98</t>
+          <t>61.52 ± 10.29</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>51.75 ± 5.24</t>
+          <t>41.60 ± 6.64</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>12.78 ± 9.30</t>
+          <t>22.76 ± 17.87</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>9.05 ± 7.04</t>
+          <t>14.26 ± 14.85</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>44.87 ± 0.02</t>
+          <t>47.86 ± 0.03</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>55.13 ± 0.02</t>
+          <t>52.14 ± 0.03</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>44.90 ± 0.00</t>
+          <t>47.89 ± 0.00</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>55.10 ± 0.00</t>
+          <t>52.11 ± 0.00</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4658,72 +4658,72 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>45.95 ± 4.53</t>
+          <t>56.71 ± 5.84</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>46.82 ± 4.61</t>
+          <t>56.96 ± 5.68</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>46.57 ± 4.66</t>
+          <t>56.60 ± 6.14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>45.61 ± 5.36</t>
+          <t>57.71 ± 6.54</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>43.08 ± 3.96</t>
+          <t>53.51 ± 4.46</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-8.12 ± 9.10</t>
+          <t>13.37 ± 11.61</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>50.91 ± 5.27</t>
+          <t>65.51 ± 4.21</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>53.84 ± 4.61</t>
+          <t>43.20 ± 5.41</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
+          <t>4.98 ± 14.95</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>44.87 ± 0.02</t>
+          <t>47.86 ± 0.03</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>55.13 ± 0.02</t>
+          <t>52.14 ± 0.03</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>44.90 ± 0.00</t>
+          <t>47.89 ± 0.00</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>55.10 ± 0.00</t>
+          <t>52.11 ± 0.00</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4766,72 +4766,72 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>45.07 ± 6.84</t>
+          <t>56.59 ± 6.88</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>46.04 ± 6.76</t>
+          <t>56.96 ± 6.81</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>45.65 ± 6.88</t>
+          <t>56.32 ± 7.47</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>44.01 ± 10.28</t>
+          <t>61.01 ± 9.07</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>44.20 ± 9.43</t>
+          <t>60.75 ± 7.87</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-9.92 ± 13.83</t>
+          <t>13.19 ± 13.71</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>44.21 ± 9.46</t>
+          <t>61.00 ± 7.56</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>55.26 ± 7.08</t>
+          <t>43.12 ± 6.57</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>11.00 ± 8.43</t>
+          <t>23.93 ± 11.82</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>7.89 ± 6.66</t>
+          <t>16.56 ± 9.50</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>44.87 ± 0.02</t>
+          <t>47.86 ± 0.03</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>55.13 ± 0.02</t>
+          <t>52.14 ± 0.03</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>44.90 ± 0.00</t>
+          <t>47.89 ± 0.00</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>55.10 ± 0.00</t>
+          <t>52.11 ± 0.00</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4874,72 +4874,72 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>54.42 ± 7.45</t>
+          <t>66.43 ± 10.28</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>57.77 ± 7.05</t>
+          <t>66.81 ± 10.04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>53.80 ± 7.84</t>
+          <t>65.91 ± 10.70</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>54.64 ± 12.20</t>
+          <t>70.21 ± 13.15</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>53.08 ± 13.72</t>
+          <t>68.51 ± 13.56</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>9.23 ± 15.91</t>
+          <t>32.91 ± 20.35</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>53.06 ± 13.72</t>
+          <t>68.46 ± 13.60</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>46.52 ± 8.93</t>
+          <t>34.61 ± 10.83</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>20.00 ± 15.39</t>
+          <t>35.92 ± 20.73</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>15.14 ± 12.86</t>
+          <t>25.57 ± 18.03</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>44.28 ± 0.03</t>
+          <t>47.44 ± 0.02</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>55.72 ± 0.03</t>
+          <t>52.56 ± 0.02</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>44.30 ± 0.00</t>
+          <t>47.47 ± 0.00</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>55.70 ± 0.00</t>
+          <t>52.53 ± 0.00</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4982,72 +4982,72 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>49.53 ± 5.56</t>
+          <t>60.80 ± 10.81</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>51.12 ± 5.12</t>
+          <t>61.14 ± 10.64</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>50.33 ± 5.37</t>
+          <t>60.57 ± 11.11</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>47.70 ± 7.00</t>
+          <t>62.37 ± 13.65</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>45.78 ± 7.07</t>
+          <t>59.73 ± 12.86</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-1.01 ± 11.37</t>
+          <t>21.61 ± 21.58</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>47.22 ± 8.32</t>
+          <t>63.20 ± 13.04</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>51.10 ± 4.57</t>
+          <t>39.98 ± 10.81</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>13.54 ± 9.89</t>
+          <t>28.26 ± 18.59</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>8.44 ± 6.51</t>
+          <t>14.74 ± 16.31</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>44.28 ± 0.03</t>
+          <t>47.44 ± 0.02</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>55.72 ± 0.03</t>
+          <t>52.56 ± 0.02</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>44.30 ± 0.00</t>
+          <t>47.47 ± 0.00</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>55.70 ± 0.00</t>
+          <t>52.53 ± 0.00</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5090,72 +5090,72 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>46.47 ± 6.92</t>
+          <t>58.30 ± 7.95</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>47.24 ± 6.48</t>
+          <t>58.37 ± 8.05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>47.11 ± 6.42</t>
+          <t>58.06 ± 8.35</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>46.20 ± 7.50</t>
+          <t>59.21 ± 8.79</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>43.28 ± 5.17</t>
+          <t>54.51 ± 6.68</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-7.09 ± 13.75</t>
+          <t>16.59 ± 15.82</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>51.56 ± 7.57</t>
+          <t>66.22 ± 6.62</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>53.49 ± 5.62</t>
+          <t>41.48 ± 8.02</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
+          <t>7.70 ± 15.76</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>44.28 ± 0.03</t>
+          <t>47.44 ± 0.02</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>55.72 ± 0.03</t>
+          <t>52.56 ± 0.02</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>44.30 ± 0.00</t>
+          <t>47.47 ± 0.00</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>55.70 ± 0.00</t>
+          <t>52.53 ± 0.00</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5198,72 +5198,72 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>45.41 ± 8.81</t>
+          <t>58.81 ± 8.70</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>46.35 ± 8.24</t>
+          <t>58.97 ± 8.82</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>46.10 ± 8.23</t>
+          <t>58.45 ± 9.37</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>44.60 ± 10.76</t>
+          <t>62.60 ± 12.95</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>43.12 ± 9.02</t>
+          <t>62.68 ± 11.88</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-9.25 ± 17.56</t>
+          <t>17.64 ± 17.27</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>43.16 ± 8.99</t>
+          <t>62.74 ± 11.75</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>54.09 ± 8.27</t>
+          <t>41.43 ± 8.54</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>10.36 ± 7.90</t>
+          <t>27.87 ± 12.62</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>6.36 ± 5.07</t>
+          <t>20.30 ± 11.89</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>44.28 ± 0.03</t>
+          <t>47.44 ± 0.02</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>55.72 ± 0.03</t>
+          <t>52.56 ± 0.02</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>44.30 ± 0.00</t>
+          <t>47.47 ± 0.00</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>55.70 ± 0.00</t>
+          <t>52.53 ± 0.00</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5306,72 +5306,72 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>55.06 ± 5.72</t>
+          <t>63.03 ± 6.10</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>62.55 ± 5.39</t>
+          <t>66.02 ± 6.22</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>57.21 ± 6.80</t>
+          <t>64.58 ± 6.06</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>53.91 ± 11.11</t>
+          <t>68.56 ± 8.07</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>46.67 ± 11.57</t>
+          <t>60.68 ± 9.92</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>11.22 ± 12.77</t>
+          <t>27.17 ± 12.52</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>46.65 ± 11.58</t>
+          <t>60.62 ± 9.92</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>46.82 ± 8.64</t>
+          <t>36.33 ± 7.04</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>20.90 ± 12.61</t>
+          <t>30.35 ± 14.16</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>13.86 ± 11.38</t>
+          <t>18.66 ± 13.09</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>38.60 ± 0.02</t>
+          <t>41.99 ± 0.03</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>61.40 ± 0.02</t>
+          <t>58.01 ± 0.03</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>38.63 ± 0.00</t>
+          <t>42.03 ± 0.00</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>61.37 ± 0.00</t>
+          <t>57.97 ± 0.00</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5414,72 +5414,72 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>49.75 ± 4.67</t>
+          <t>58.80 ± 6.36</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>54.17 ± 4.72</t>
+          <t>61.08 ± 6.15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>52.72 ± 5.01</t>
+          <t>60.14 ± 6.32</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>47.90 ± 7.86</t>
+          <t>60.12 ± 7.54</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>39.42 ± 6.45</t>
+          <t>51.64 ± 7.83</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-0.53 ± 9.74</t>
+          <t>17.94 ± 12.77</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>40.47 ± 7.07</t>
+          <t>55.46 ± 7.99</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>51.31 ± 5.36</t>
+          <t>42.23 ± 6.06</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>11.01 ± 7.10</t>
+          <t>19.23 ± 11.62</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>5.81 ± 6.11</t>
+          <t>10.20 ± 9.44</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>38.60 ± 0.02</t>
+          <t>41.99 ± 0.03</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>61.40 ± 0.02</t>
+          <t>58.01 ± 0.03</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>38.63 ± 0.00</t>
+          <t>42.03 ± 0.00</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>61.37 ± 0.00</t>
+          <t>57.97 ± 0.00</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5522,72 +5522,72 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>47.09 ± 4.03</t>
+          <t>54.86 ± 6.14</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>49.67 ± 4.38</t>
+          <t>55.88 ± 5.69</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>49.69 ± 4.39</t>
+          <t>55.57 ± 5.88</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>46.59 ± 4.58</t>
+          <t>55.41 ± 6.20</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>37.55 ± 2.43</t>
+          <t>45.84 ± 4.94</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-5.82 ± 7.98</t>
+          <t>9.57 ± 12.19</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>45.82 ± 3.63</t>
+          <t>57.40 ± 6.60</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>53.46 ± 4.06</t>
+          <t>45.33 ± 5.61</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
+          <t>3.62 ± 10.85</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>38.60 ± 0.02</t>
+          <t>41.99 ± 0.03</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>61.40 ± 0.02</t>
+          <t>58.01 ± 0.03</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>38.63 ± 0.00</t>
+          <t>42.03 ± 0.00</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>61.37 ± 0.00</t>
+          <t>57.97 ± 0.00</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5630,72 +5630,72 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>45.35 ± 5.21</t>
+          <t>54.84 ± 5.72</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>48.88 ± 5.78</t>
+          <t>55.69 ± 5.82</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>48.34 ± 5.56</t>
+          <t>55.26 ± 5.93</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>42.72 ± 7.98</t>
+          <t>59.75 ± 7.13</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>38.13 ± 5.73</t>
+          <t>52.75 ± 7.70</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-9.35 ± 10.44</t>
+          <t>9.57 ± 11.59</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>38.06 ± 5.70</t>
+          <t>52.85 ± 7.63</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>56.18 ± 5.15</t>
+          <t>44.60 ± 5.12</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>11.43 ± 5.52</t>
+          <t>18.48 ± 8.61</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>7.90 ± 4.72</t>
+          <t>12.73 ± 8.03</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>38.60 ± 0.02</t>
+          <t>41.99 ± 0.03</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>61.40 ± 0.02</t>
+          <t>58.01 ± 0.03</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>38.63 ± 0.00</t>
+          <t>42.03 ± 0.00</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>61.37 ± 0.00</t>
+          <t>57.97 ± 0.00</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5738,72 +5738,72 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>54.60 ± 4.39</t>
+          <t>63.56 ± 7.49</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>65.80 ± 4.72</t>
+          <t>68.60 ± 6.78</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>59.69 ± 4.71</t>
+          <t>66.39 ± 7.47</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>54.80 ± 7.04</t>
+          <t>70.89 ± 10.84</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>42.38 ± 6.66</t>
+          <t>59.25 ± 14.14</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>10.73 ± 9.91</t>
+          <t>28.73 ± 15.64</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>42.35 ± 6.66</t>
+          <t>59.19 ± 14.14</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>46.93 ± 4.46</t>
+          <t>32.22 ± 10.05</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>20.60 ± 8.86</t>
+          <t>31.83 ± 25.37</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>11.90 ± 6.10</t>
+          <t>21.41 ± 18.38</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>35.22 ± 0.03</t>
+          <t>38.27 ± 0.03</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>64.78 ± 0.03</t>
+          <t>61.73 ± 0.03</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>35.25 ± 0.00</t>
+          <t>38.29 ± 0.00</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>64.75 ± 0.00</t>
+          <t>61.71 ± 0.00</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5846,72 +5846,72 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>51.92 ± 3.40</t>
+          <t>58.76 ± 7.53</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>59.37 ± 3.23</t>
+          <t>62.69 ± 7.03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>57.32 ± 3.32</t>
+          <t>61.32 ± 7.54</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>51.61 ± 6.12</t>
+          <t>60.67 ± 9.15</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>38.54 ± 6.95</t>
+          <t>48.40 ± 11.37</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>4.00 ± 7.00</t>
+          <t>17.95 ± 15.56</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>39.73 ± 7.82</t>
+          <t>51.36 ± 11.55</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>49.28 ± 4.45</t>
+          <t>41.59 ± 6.83</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>13.30 ± 6.79</t>
+          <t>20.71 ± 17.38</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>8.24 ± 6.55</t>
+          <t>12.80 ± 16.32</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>35.22 ± 0.03</t>
+          <t>38.27 ± 0.03</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>64.78 ± 0.03</t>
+          <t>61.73 ± 0.03</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>35.25 ± 0.00</t>
+          <t>38.29 ± 0.00</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>64.75 ± 0.00</t>
+          <t>61.71 ± 0.00</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5954,47 +5954,47 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>46.96 ± 5.55</t>
+          <t>58.01 ± 5.03</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>51.87 ± 4.85</t>
+          <t>60.09 ± 4.94</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>51.71 ± 4.24</t>
+          <t>60.07 ± 4.80</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>47.27 ± 7.00</t>
+          <t>59.89 ± 5.54</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>34.82 ± 5.28</t>
+          <t>45.36 ± 4.58</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-5.80 ± 10.70</t>
+          <t>15.90 ± 9.85</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>42.07 ± 7.93</t>
+          <t>57.80 ± 5.35</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>52.04 ± 5.82</t>
+          <t>41.70 ± 5.12</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>3.00 ± 9.01</t>
+          <t>7.59 ± 15.32</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6004,22 +6004,22 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>35.22 ± 0.03</t>
+          <t>38.27 ± 0.03</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>64.78 ± 0.03</t>
+          <t>61.73 ± 0.03</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>35.25 ± 0.00</t>
+          <t>38.29 ± 0.00</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>64.75 ± 0.00</t>
+          <t>61.71 ± 0.00</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6062,72 +6062,72 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>46.79 ± 6.58</t>
+          <t>58.61 ± 8.77</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>52.98 ± 5.17</t>
+          <t>60.93 ± 8.23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>52.04 ± 4.96</t>
+          <t>60.63 ± 8.24</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>45.67 ± 11.74</t>
+          <t>65.16 ± 9.39</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>36.51 ± 9.65</t>
+          <t>51.29 ± 8.94</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-6.45 ± 13.31</t>
+          <t>17.07 ± 17.19</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>36.49 ± 9.65</t>
+          <t>51.22 ± 8.93</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>54.12 ± 8.76</t>
+          <t>40.10 ± 7.97</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>10.90 ± 7.14</t>
+          <t>20.88 ± 11.44</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>8.02 ± 6.02</t>
+          <t>10.99 ± 6.98</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>35.22 ± 0.03</t>
+          <t>38.27 ± 0.03</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>64.78 ± 0.03</t>
+          <t>61.73 ± 0.03</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>35.25 ± 0.00</t>
+          <t>38.29 ± 0.00</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>64.75 ± 0.00</t>
+          <t>61.71 ± 0.00</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6170,72 +6170,72 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>52.97 ± 4.76</t>
+          <t>62.85 ± 7.61</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>65.61 ± 3.39</t>
+          <t>69.28 ± 7.25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>58.96 ± 3.89</t>
+          <t>66.63 ± 7.97</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>50.61 ± 10.74</t>
+          <t>71.12 ± 13.86</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>38.35 ± 10.40</t>
+          <t>60.81 ± 15.87</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>6.73 ± 11.01</t>
+          <t>27.79 ± 16.61</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>38.32 ± 10.40</t>
+          <t>60.75 ± 15.88</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>49.26 ± 8.49</t>
+          <t>33.63 ± 11.39</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>16.01 ± 9.77</t>
+          <t>38.13 ± 21.92</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>9.44 ± 8.44</t>
+          <t>28.19 ± 18.48</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>34.01 ± 0.03</t>
+          <t>36.91 ± 0.03</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>65.99 ± 0.03</t>
+          <t>63.09 ± 0.03</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>34.07 ± 0.00</t>
+          <t>36.94 ± 0.00</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>65.93 ± 0.00</t>
+          <t>63.06 ± 0.00</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6278,72 +6278,72 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>51.11 ± 5.76</t>
+          <t>57.63 ± 8.95</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>59.71 ± 4.18</t>
+          <t>62.72 ± 9.52</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>57.49 ± 4.38</t>
+          <t>61.16 ± 9.61</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>49.62 ± 8.15</t>
+          <t>59.43 ± 11.82</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>36.43 ± 8.02</t>
+          <t>48.32 ± 12.66</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2.29 ± 12.36</t>
+          <t>16.15 ± 18.95</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>37.53 ± 9.67</t>
+          <t>51.19 ± 13.19</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>50.48 ± 5.92</t>
+          <t>42.96 ± 8.52</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>11.58 ± 7.30</t>
+          <t>24.18 ± 17.06</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>7.45 ± 5.61</t>
+          <t>16.09 ± 14.75</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>34.01 ± 0.03</t>
+          <t>36.91 ± 0.03</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>65.99 ± 0.03</t>
+          <t>63.09 ± 0.03</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>34.07 ± 0.00</t>
+          <t>36.94 ± 0.00</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>65.93 ± 0.00</t>
+          <t>63.06 ± 0.00</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6386,47 +6386,47 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>47.51 ± 4.49</t>
+          <t>53.69 ± 8.94</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>53.84 ± 4.81</t>
+          <t>56.70 ± 9.13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>53.29 ± 3.72</t>
+          <t>56.47 ± 9.20</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>46.93 ± 5.98</t>
+          <t>54.85 ± 8.56</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>33.73 ± 5.31</t>
+          <t>41.31 ± 7.31</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-4.77 ± 9.25</t>
+          <t>7.40 ± 18.06</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>40.08 ± 8.11</t>
+          <t>52.01 ± 8.34</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>53.01 ± 4.58</t>
+          <t>46.35 ± 7.59</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>4.49 ± 9.27</t>
+          <t>8.51 ± 17.24</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6436,22 +6436,22 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>34.01 ± 0.03</t>
+          <t>36.91 ± 0.03</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>65.99 ± 0.03</t>
+          <t>63.09 ± 0.03</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>34.07 ± 0.00</t>
+          <t>36.94 ± 0.00</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>65.93 ± 0.00</t>
+          <t>63.06 ± 0.00</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6494,72 +6494,72 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>47.57 ± 4.53</t>
+          <t>56.74 ± 8.34</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>55.34 ± 5.00</t>
+          <t>60.03 ± 9.37</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>53.52 ± 3.64</t>
+          <t>59.51 ± 9.50</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>45.49 ± 7.21</t>
+          <t>61.11 ± 10.96</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>34.61 ± 8.96</t>
+          <t>48.45 ± 10.89</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-5.00 ± 9.99</t>
+          <t>13.83 ± 17.20</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>34.65 ± 8.91</t>
+          <t>48.40 ± 10.87</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>53.49 ± 5.04</t>
+          <t>42.86 ± 7.32</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>10.90 ± 6.42</t>
+          <t>21.90 ± 11.83</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>7.13 ± 4.79</t>
+          <t>12.80 ± 8.98</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>34.01 ± 0.03</t>
+          <t>36.91 ± 0.03</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>65.99 ± 0.03</t>
+          <t>63.09 ± 0.03</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>34.07 ± 0.00</t>
+          <t>36.94 ± 0.00</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>65.93 ± 0.00</t>
+          <t>63.06 ± 0.00</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6602,72 +6602,72 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>53.33 ± 4.71</t>
+          <t>62.87 ± 7.43</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>71.12 ± 4.44</t>
+          <t>72.55 ± 7.88</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>64.31 ± 5.90</t>
+          <t>69.92 ± 7.93</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>57.20 ± 10.43</t>
+          <t>73.21 ± 11.12</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>36.88 ± 12.76</t>
+          <t>56.88 ± 14.97</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>8.32 ± 11.92</t>
+          <t>28.90 ± 16.57</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>36.83 ± 12.76</t>
+          <t>56.80 ± 14.98</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>45.10 ± 8.71</t>
+          <t>30.87 ± 9.90</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>20.32 ± 15.12</t>
+          <t>40.32 ± 23.01</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>13.12 ± 12.35</t>
+          <t>24.97 ± 20.83</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>28.48 ± 0.04</t>
+          <t>31.34 ± 0.03</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>71.52 ± 0.04</t>
+          <t>68.66 ± 0.03</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>28.52 ± 0.00</t>
+          <t>31.37 ± 0.00</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>71.48 ± 0.00</t>
+          <t>68.63 ± 0.00</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6710,72 +6710,72 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>52.83 ± 4.73</t>
+          <t>60.17 ± 8.09</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>66.40 ± 4.37</t>
+          <t>68.81 ± 8.02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>63.38 ± 5.39</t>
+          <t>66.97 ± 8.00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>54.98 ± 6.26</t>
+          <t>64.73 ± 9.79</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>33.13 ± 7.41</t>
+          <t>45.88 ± 12.15</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>6.22 ± 10.53</t>
+          <t>21.81 ± 16.80</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>34.14 ± 8.36</t>
+          <t>49.60 ± 12.52</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>46.58 ± 4.57</t>
+          <t>39.09 ± 7.56</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>16.06 ± 9.10</t>
+          <t>27.08 ± 18.57</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>8.82 ± 6.44</t>
+          <t>18.71 ± 16.24</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>28.48 ± 0.04</t>
+          <t>31.34 ± 0.03</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>71.52 ± 0.04</t>
+          <t>68.66 ± 0.03</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>28.52 ± 0.00</t>
+          <t>31.37 ± 0.00</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>71.48 ± 0.00</t>
+          <t>68.63 ± 0.00</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6818,72 +6818,72 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>47.46 ± 6.60</t>
+          <t>55.62 ± 4.88</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>58.17 ± 7.49</t>
+          <t>61.22 ± 4.33</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>57.53 ± 6.83</t>
+          <t>61.08 ± 4.63</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>47.57 ± 7.32</t>
+          <t>56.27 ± 7.12</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>29.04 ± 5.06</t>
+          <t>35.27 ± 5.56</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-4.53 ± 13.56</t>
+          <t>10.66 ± 8.88</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>34.04 ± 8.43</t>
+          <t>47.13 ± 7.69</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>51.62 ± 5.01</t>
+          <t>45.02 ± 5.92</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>7.58 ± 11.53</t>
+          <t>7.20 ± 11.35</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2.68 ± 8.03</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>28.48 ± 0.04</t>
+          <t>31.34 ± 0.03</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>71.52 ± 0.04</t>
+          <t>68.66 ± 0.03</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>28.52 ± 0.00</t>
+          <t>31.37 ± 0.00</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>71.48 ± 0.00</t>
+          <t>68.63 ± 0.00</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6926,72 +6926,72 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>46.77 ± 5.62</t>
+          <t>57.76 ± 5.74</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.21 ± 6.99</t>
+          <t>63.67 ± 5.27</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>57.81 ± 5.70</t>
+          <t>63.21 ± 5.34</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>46.10 ± 10.63</t>
+          <t>63.27 ± 6.93</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>29.31 ± 7.98</t>
+          <t>41.28 ± 7.71</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-6.22 ± 11.69</t>
+          <t>15.18 ± 10.86</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>29.26 ± 8.00</t>
+          <t>41.19 ± 7.72</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>53.19 ± 7.64</t>
+          <t>40.22 ± 5.71</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>9.56 ± 7.29</t>
+          <t>14.29 ± 8.76</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>5.85 ± 4.94</t>
+          <t>7.54 ± 7.10</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>28.48 ± 0.04</t>
+          <t>31.34 ± 0.03</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>71.52 ± 0.04</t>
+          <t>68.66 ± 0.03</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>28.52 ± 0.00</t>
+          <t>31.37 ± 0.00</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>71.48 ± 0.00</t>
+          <t>68.63 ± 0.00</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7034,72 +7034,72 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>49.61 ± 0.79</t>
+          <t>59.31 ± 9.06</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>75.63 ± 3.03</t>
+          <t>73.71 ± 6.13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>65.86 ± 3.50</t>
+          <t>70.50 ± 6.92</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>54.91 ± 6.92</t>
+          <t>71.92 ± 10.60</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>28.07 ± 6.46</t>
+          <t>47.67 ± 14.08</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-1.09 ± 2.20</t>
+          <t>20.66 ± 19.95</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>27.99 ± 6.47</t>
+          <t>47.58 ± 14.09</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>46.45 ± 4.79</t>
+          <t>32.16 ± 9.75</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>14.61 ± 9.95</t>
+          <t>31.25 ± 24.82</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>7.91 ± 8.58</t>
+          <t>19.94 ± 19.71</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>23.67 ± 0.03</t>
+          <t>26.44 ± 0.02</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>76.33 ± 0.03</t>
+          <t>73.56 ± 0.02</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>23.66 ± 0.00</t>
+          <t>26.49 ± 0.00</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>76.34 ± 0.00</t>
+          <t>73.51 ± 0.00</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7142,72 +7142,72 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>50.56 ± 2.63</t>
+          <t>55.43 ± 3.10</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>70.71 ± 3.41</t>
+          <t>69.65 ± 3.82</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>66.65 ± 3.86</t>
+          <t>67.05 ± 3.59</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>51.95 ± 5.82</t>
+          <t>57.64 ± 3.27</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>25.29 ± 3.33</t>
+          <t>33.63 ± 4.33</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1.32 ± 6.46</t>
+          <t>12.13 ± 6.76</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>25.70 ± 4.11</t>
+          <t>36.89 ± 4.90</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>48.83 ± 4.12</t>
+          <t>44.47 ± 2.38</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>10.93 ± 5.29</t>
+          <t>19.18 ± 5.02</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>6.03 ± 3.47</t>
+          <t>12.98 ± 7.62</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>23.67 ± 0.03</t>
+          <t>26.44 ± 0.02</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>76.33 ± 0.03</t>
+          <t>73.56 ± 0.02</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>23.66 ± 0.00</t>
+          <t>26.49 ± 0.00</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>76.34 ± 0.00</t>
+          <t>73.51 ± 0.00</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>47.53 ± 5.46</t>
+          <t>56.78 ± 5.93</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>62.50 ± 6.31</t>
+          <t>66.06 ± 5.25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>62.20 ± 5.58</t>
+          <t>65.98 ± 4.96</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>47.24 ± 6.26</t>
+          <t>57.97 ± 6.66</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>23.61 ± 3.24</t>
+          <t>32.55 ± 5.16</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-4.51 ± 11.42</t>
+          <t>13.44 ± 11.58</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>27.99 ± 6.80</t>
+          <t>45.24 ± 7.45</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>51.73 ± 4.39</t>
+          <t>43.61 ± 5.97</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>10.74 ± 10.04</t>
+          <t>13.52 ± 17.35</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2.00 ± 6.01</t>
+          <t>2.16 ± 6.49</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>23.67 ± 0.03</t>
+          <t>26.44 ± 0.02</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>76.33 ± 0.03</t>
+          <t>73.56 ± 0.02</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>23.66 ± 0.00</t>
+          <t>26.49 ± 0.00</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>76.34 ± 0.00</t>
+          <t>73.51 ± 0.00</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7358,72 +7358,72 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>46.96 ± 5.14</t>
+          <t>55.09 ± 7.36</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>66.04 ± 6.30</t>
+          <t>65.71 ± 5.52</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>63.31 ± 5.29</t>
+          <t>65.20 ± 4.92</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>45.09 ± 12.88</t>
+          <t>62.19 ± 10.41</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>23.31 ± 7.29</t>
+          <t>37.82 ± 11.36</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-6.20 ± 11.09</t>
+          <t>10.29 ± 14.69</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>23.14 ± 7.42</t>
+          <t>37.78 ± 11.48</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>53.04 ± 8.41</t>
+          <t>41.37 ± 7.50</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>6.86 ± 7.21</t>
+          <t>16.99 ± 10.35</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>4.11 ± 5.85</t>
+          <t>11.09 ± 8.10</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>23.67 ± 0.03</t>
+          <t>26.44 ± 0.02</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>76.33 ± 0.03</t>
+          <t>73.56 ± 0.02</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>23.66 ± 0.00</t>
+          <t>26.49 ± 0.00</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>76.34 ± 0.00</t>
+          <t>73.51 ± 0.00</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7466,72 +7466,72 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>49.77 ± 0.46</t>
+          <t>58.82 ± 12.92</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>79.44 ± 4.01</t>
+          <t>75.49 ± 9.29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>70.72 ± 5.56</t>
+          <t>72.47 ± 10.44</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>54.10 ± 10.75</t>
+          <t>71.21 ± 17.32</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>23.58 ± 8.67</t>
+          <t>44.94 ± 22.41</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-0.69 ± 1.38</t>
+          <t>18.49 ± 27.94</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>23.51 ± 8.66</t>
+          <t>44.84 ± 22.41</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>47.00 ± 7.60</t>
+          <t>31.89 ± 15.29</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>11.64 ± 8.22</t>
+          <t>33.01 ± 34.21</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>5.56 ± 5.30</t>
+          <t>24.30 ± 28.64</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>20.19 ± 0.04</t>
+          <t>22.55 ± 0.03</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>79.81 ± 0.04</t>
+          <t>77.45 ± 0.03</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>20.26 ± 0.00</t>
+          <t>22.58 ± 0.00</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>79.74 ± 0.00</t>
+          <t>77.42 ± 0.00</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7574,72 +7574,72 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>49.77 ± 2.25</t>
+          <t>54.77 ± 8.53</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>75.29 ± 3.60</t>
+          <t>73.70 ± 5.45</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>70.66 ± 4.33</t>
+          <t>70.70 ± 6.77</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>51.31 ± 8.52</t>
+          <t>56.79 ± 9.89</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>21.58 ± 6.97</t>
+          <t>32.37 ± 13.12</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-0.44 ± 5.67</t>
+          <t>10.70 ± 19.34</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>21.64 ± 7.86</t>
+          <t>33.78 ± 14.95</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>48.94 ± 6.05</t>
+          <t>44.75 ± 6.62</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>9.55 ± 5.59</t>
+          <t>20.55 ± 17.65</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>4.80 ± 3.24</t>
+          <t>14.63 ± 14.05</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>20.19 ± 0.04</t>
+          <t>22.55 ± 0.03</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>79.81 ± 0.04</t>
+          <t>77.45 ± 0.03</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>20.26 ± 0.00</t>
+          <t>22.58 ± 0.00</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>79.74 ± 0.00</t>
+          <t>77.42 ± 0.00</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7682,72 +7682,72 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>48.72 ± 5.37</t>
+          <t>54.06 ± 8.77</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.44 ± 5.47</t>
+          <t>67.30 ± 7.11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>68.40 ± 5.25</t>
+          <t>67.40 ± 6.78</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>48.41 ± 7.03</t>
+          <t>55.47 ± 10.69</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>21.52 ± 7.06</t>
+          <t>28.06 ± 8.78</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-2.01 ± 11.93</t>
+          <t>7.87 ± 17.77</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>24.67 ± 11.43</t>
+          <t>36.77 ± 14.03</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>50.96 ± 4.64</t>
+          <t>45.31 ± 8.32</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>11.27 ± 9.81</t>
+          <t>17.25 ± 17.43</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>6.58 ± 9.42</t>
+          <t>9.03 ± 14.41</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>20.19 ± 0.04</t>
+          <t>22.55 ± 0.03</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>79.81 ± 0.04</t>
+          <t>77.45 ± 0.03</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>20.26 ± 0.00</t>
+          <t>22.58 ± 0.00</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>79.74 ± 0.00</t>
+          <t>77.42 ± 0.00</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7790,72 +7790,72 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>48.05 ± 3.70</t>
+          <t>51.95 ± 5.91</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>72.98 ± 4.55</t>
+          <t>67.58 ± 5.80</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>69.11 ± 4.69</t>
+          <t>66.66 ± 5.60</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>45.66 ± 12.99</t>
+          <t>61.75 ± 13.85</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>20.84 ± 10.03</t>
+          <t>29.89 ± 9.46</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-4.45 ± 9.06</t>
+          <t>3.77 ± 12.16</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>20.65 ± 10.15</t>
+          <t>29.73 ± 9.44</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>53.48 ± 9.45</t>
+          <t>41.55 ± 10.19</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>8.19 ± 9.37</t>
+          <t>11.75 ± 8.32</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>4.51 ± 6.10</t>
+          <t>7.34 ± 6.24</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>20.19 ± 0.04</t>
+          <t>22.55 ± 0.03</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>79.81 ± 0.04</t>
+          <t>77.45 ± 0.03</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>20.26 ± 0.00</t>
+          <t>22.58 ± 0.00</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>79.74 ± 0.00</t>
+          <t>77.42 ± 0.00</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7898,72 +7898,72 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>49.61 ± 1.04</t>
+          <t>61.69 ± 12.79</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>83.02 ± 3.61</t>
+          <t>79.48 ± 7.83</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>75.97 ± 5.02</t>
+          <t>77.69 ± 8.52</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>51.74 ± 8.40</t>
+          <t>76.45 ± 15.80</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>17.79 ± 6.19</t>
+          <t>47.99 ± 22.09</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-1.05 ± 2.69</t>
+          <t>24.97 ± 26.17</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>17.75 ± 6.18</t>
+          <t>47.88 ± 22.07</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>48.53 ± 5.74</t>
+          <t>27.25 ± 14.05</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>9.40 ± 6.80</t>
+          <t>42.36 ± 35.97</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>4.54 ± 4.17</t>
+          <t>35.21 ± 30.00</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>16.30 ± 0.04</t>
+          <t>18.63 ± 0.04</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>83.70 ± 0.04</t>
+          <t>81.37 ± 0.04</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>16.41 ± 0.00</t>
+          <t>18.76 ± 0.00</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>83.59 ± 0.00</t>
+          <t>81.24 ± 0.00</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8006,72 +8006,72 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>49.58 ± 1.55</t>
+          <t>57.74 ± 9.62</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>79.78 ± 3.93</t>
+          <t>78.94 ± 6.23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>75.46 ± 4.70</t>
+          <t>76.43 ± 6.74</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>49.65 ± 7.18</t>
+          <t>61.49 ± 11.78</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>16.50 ± 4.02</t>
+          <t>31.86 ± 13.34</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-0.94 ± 3.98</t>
+          <t>17.20 ± 18.85</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>16.34 ± 4.37</t>
+          <t>34.88 ± 16.00</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>49.93 ± 5.59</t>
+          <t>41.39 ± 9.92</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>9.03 ± 3.91</t>
+          <t>27.27 ± 20.43</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>4.53 ± 2.40</t>
+          <t>20.69 ± 17.58</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>16.30 ± 0.04</t>
+          <t>18.63 ± 0.04</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>83.70 ± 0.04</t>
+          <t>81.37 ± 0.04</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>16.41 ± 0.00</t>
+          <t>18.76 ± 0.00</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>83.59 ± 0.00</t>
+          <t>81.24 ± 0.00</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8114,72 +8114,72 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>48.64 ± 5.24</t>
+          <t>59.14 ± 10.38</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>74.12 ± 6.17</t>
+          <t>74.94 ± 7.83</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>73.02 ± 5.87</t>
+          <t>74.47 ± 6.92</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>47.25 ± 6.10</t>
+          <t>61.83 ± 11.60</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>16.95 ± 4.00</t>
+          <t>27.74 ± 10.55</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-2.75 ± 11.04</t>
+          <t>16.78 ± 18.38</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>18.32 ± 8.94</t>
+          <t>40.03 ± 15.94</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>51.57 ± 3.66</t>
+          <t>39.74 ± 10.31</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>8.79 ± 9.51</t>
+          <t>28.31 ± 25.04</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>4.76 ± 8.11</t>
+          <t>4.67 ± 8.19</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>16.30 ± 0.04</t>
+          <t>18.63 ± 0.04</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>83.70 ± 0.04</t>
+          <t>81.37 ± 0.04</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>16.41 ± 0.00</t>
+          <t>18.76 ± 0.00</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>83.59 ± 0.00</t>
+          <t>81.24 ± 0.00</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8222,72 +8222,72 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>48.47 ± 4.90</t>
+          <t>56.81 ± 8.78</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>77.25 ± 6.26</t>
+          <t>75.14 ± 6.87</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>74.11 ± 6.15</t>
+          <t>74.24 ± 6.19</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>47.00 ± 12.24</t>
+          <t>71.01 ± 12.33</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>17.37 ± 8.90</t>
+          <t>34.14 ± 16.64</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-3.31 ± 11.84</t>
+          <t>13.40 ± 17.20</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>17.19 ± 9.09</t>
+          <t>34.13 ± 16.65</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>51.90 ± 9.75</t>
+          <t>32.33 ± 9.82</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>6.26 ± 8.74</t>
+          <t>20.73 ± 17.66</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>4.44 ± 8.14</t>
+          <t>13.48 ± 16.43</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>16.30 ± 0.04</t>
+          <t>18.63 ± 0.04</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>83.70 ± 0.04</t>
+          <t>81.37 ± 0.04</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>16.41 ± 0.00</t>
+          <t>18.76 ± 0.00</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>83.59 ± 0.00</t>
+          <t>81.24 ± 0.00</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8330,72 +8330,72 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>49.45 ± 1.47</t>
+          <t>64.26 ± 13.65</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>83.81 ± 3.83</t>
+          <t>82.55 ± 6.04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>77.33 ± 4.78</t>
+          <t>80.64 ± 7.85</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>50.97 ± 13.27</t>
+          <t>79.66 ± 15.52</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>17.09 ± 7.56</t>
+          <t>48.84 ± 24.84</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-1.36 ± 3.42</t>
+          <t>29.35 ± 27.73</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>16.99 ± 7.55</t>
+          <t>48.74 ± 24.87</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>48.70 ± 9.81</t>
+          <t>24.26 ± 13.52</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>8.16 ± 8.53</t>
+          <t>43.02 ± 33.45</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>4.60 ± 5.84</t>
+          <t>30.46 ± 31.16</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>15.23 ± 0.04</t>
+          <t>17.65 ± 0.04</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>84.77 ± 0.04</t>
+          <t>82.35 ± 0.04</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>15.30 ± 0.00</t>
+          <t>17.75 ± 0.00</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>84.70 ± 0.00</t>
+          <t>82.25 ± 0.00</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8438,72 +8438,72 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>49.48 ± 1.98</t>
+          <t>59.06 ± 10.62</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>81.30 ± 4.27</t>
+          <t>81.28 ± 4.72</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>76.90 ± 5.11</t>
+          <t>78.73 ± 5.99</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>49.14 ± 9.73</t>
+          <t>64.98 ± 11.88</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>15.82 ± 4.93</t>
+          <t>33.29 ± 16.78</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-1.30 ± 5.64</t>
+          <t>19.71 ± 21.21</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>15.53 ± 5.78</t>
+          <t>36.09 ± 18.68</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>50.25 ± 7.41</t>
+          <t>38.06 ± 9.75</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>9.97 ± 8.94</t>
+          <t>29.98 ± 20.44</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>4.22 ± 5.53</t>
+          <t>20.02 ± 18.42</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>15.23 ± 0.04</t>
+          <t>17.65 ± 0.04</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>84.77 ± 0.04</t>
+          <t>82.35 ± 0.04</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>15.30 ± 0.00</t>
+          <t>17.75 ± 0.00</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>84.70 ± 0.00</t>
+          <t>82.25 ± 0.00</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8546,72 +8546,72 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>48.83 ± 3.86</t>
+          <t>59.53 ± 10.65</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>75.17 ± 6.01</t>
+          <t>77.96 ± 7.25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>74.35 ± 5.76</t>
+          <t>77.50 ± 6.47</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>48.21 ± 4.38</t>
+          <t>60.36 ± 11.00</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>15.36 ± 3.11</t>
+          <t>30.32 ± 16.34</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-1.97 ± 8.01</t>
+          <t>20.66 ± 24.47</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>17.74 ± 4.84</t>
+          <t>40.85 ± 20.67</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>51.07 ± 2.60</t>
+          <t>42.62 ± 7.95</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>10.42 ± 5.02</t>
+          <t>27.19 ± 21.32</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>3.25 ± 4.76</t>
+          <t>18.91 ± 23.58</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>15.23 ± 0.04</t>
+          <t>17.65 ± 0.04</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>84.77 ± 0.04</t>
+          <t>82.35 ± 0.04</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>15.30 ± 0.00</t>
+          <t>17.75 ± 0.00</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>84.70 ± 0.00</t>
+          <t>82.25 ± 0.00</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8654,72 +8654,72 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>47.68 ± 3.66</t>
+          <t>58.28 ± 9.74</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>77.47 ± 5.92</t>
+          <t>77.94 ± 6.61</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>74.87 ± 5.76</t>
+          <t>77.11 ± 6.05</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>48.20 ± 14.26</t>
+          <t>75.02 ± 15.58</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>15.42 ± 3.57</t>
+          <t>41.56 ± 28.36</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-5.09 ± 8.02</t>
+          <t>18.55 ± 22.60</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>15.04 ± 3.73</t>
+          <t>41.54 ± 28.36</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>50.75 ± 11.36</t>
+          <t>29.00 ± 13.84</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>6.07 ± 6.07</t>
+          <t>32.03 ± 35.64</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>3.39 ± 5.09</t>
+          <t>25.38 ± 33.27</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>15.23 ± 0.04</t>
+          <t>17.65 ± 0.04</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>84.77 ± 0.04</t>
+          <t>82.35 ± 0.04</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>15.30 ± 0.00</t>
+          <t>17.75 ± 0.00</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>84.70 ± 0.00</t>
+          <t>82.25 ± 0.00</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8762,72 +8762,72 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>49.67 ± 0.74</t>
+          <t>61.74 ± 14.30</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>86.57 ± 1.24</t>
+          <t>83.33 ± 7.51</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>80.88 ± 1.27</t>
+          <t>81.37 ± 8.85</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>49.42 ± 14.88</t>
+          <t>76.94 ± 19.89</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>14.14 ± 6.13</t>
+          <t>46.24 ± 26.77</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-0.96 ± 2.03</t>
+          <t>25.26 ± 30.45</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>14.03 ± 6.07</t>
+          <t>46.14 ± 26.81</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>50.65 ± 11.53</t>
+          <t>27.16 ± 18.08</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>8.66 ± 11.41</t>
+          <t>38.14 ± 36.92</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>4.33 ± 6.64</t>
+          <t>30.58 ± 34.48</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>12.84 ± 0.01</t>
+          <t>15.57 ± 0.03</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>87.16 ± 0.01</t>
+          <t>84.43 ± 0.03</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>12.84 ± 0.00</t>
+          <t>15.69 ± 0.00</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>87.16 ± 0.00</t>
+          <t>84.31 ± 0.00</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8870,72 +8870,72 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>49.33 ± 1.32</t>
+          <t>54.76 ± 9.63</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>83.97 ± 1.72</t>
+          <t>81.32 ± 6.52</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>80.01 ± 1.81</t>
+          <t>78.51 ± 7.39</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>47.36 ± 10.33</t>
+          <t>59.65 ± 12.83</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>12.95 ± 2.08</t>
+          <t>26.75 ± 13.55</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-1.86 ± 3.71</t>
+          <t>11.68 ± 22.54</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>12.32 ± 3.19</t>
+          <t>28.07 ± 15.53</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>51.54 ± 8.71</t>
+          <t>42.21 ± 9.89</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>7.66 ± 5.92</t>
+          <t>22.55 ± 22.18</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>3.10 ± 2.76</t>
+          <t>15.33 ± 18.73</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>12.84 ± 0.01</t>
+          <t>15.57 ± 0.03</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>87.16 ± 0.01</t>
+          <t>84.43 ± 0.03</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>12.84 ± 0.00</t>
+          <t>15.69 ± 0.00</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>87.16 ± 0.00</t>
+          <t>84.31 ± 0.00</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8978,72 +8978,72 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>48.87 ± 5.22</t>
+          <t>53.66 ± 8.11</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>78.63 ± 4.97</t>
+          <t>77.23 ± 6.55</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>77.77 ± 3.48</t>
+          <t>76.37 ± 5.82</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>48.30 ± 7.48</t>
+          <t>54.02 ± 9.13</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>13.81 ± 1.99</t>
+          <t>21.24 ± 10.39</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-1.45 ± 10.38</t>
+          <t>8.04 ± 18.63</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>15.25 ± 7.15</t>
+          <t>28.17 ± 18.17</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>50.86 ± 4.52</t>
+          <t>47.12 ± 5.83</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>9.68 ± 9.70</t>
+          <t>16.47 ± 16.89</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>5.49 ± 6.41</t>
+          <t>9.09 ± 15.75</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>12.84 ± 0.01</t>
+          <t>15.57 ± 0.03</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>87.16 ± 0.01</t>
+          <t>84.43 ± 0.03</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>12.84 ± 0.00</t>
+          <t>15.69 ± 0.00</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>87.16 ± 0.00</t>
+          <t>84.31 ± 0.00</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9086,72 +9086,72 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>48.00 ± 3.74</t>
+          <t>51.16 ± 6.33</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>80.87 ± 4.65</t>
+          <t>77.24 ± 6.86</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>78.47 ± 3.01</t>
+          <t>75.70 ± 5.53</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>52.95 ± 22.82</t>
+          <t>68.79 ± 19.14</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>16.69 ± 6.19</t>
+          <t>31.89 ± 24.55</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-3.67 ± 8.21</t>
+          <t>3.57 ± 16.20</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>15.59 ± 7.34</t>
+          <t>31.88 ± 24.53</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>47.08 ± 17.89</t>
+          <t>32.26 ± 17.39</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>8.00 ± 10.36</t>
+          <t>24.61 ± 30.64</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>3.44 ± 6.31</t>
+          <t>12.66 ± 29.45</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>12.84 ± 0.01</t>
+          <t>15.57 ± 0.03</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>87.16 ± 0.01</t>
+          <t>84.43 ± 0.03</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>12.84 ± 0.00</t>
+          <t>15.69 ± 0.00</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>87.16 ± 0.00</t>
+          <t>84.31 ± 0.00</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9194,72 +9194,72 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>54.89 ± 15.04</t>
+          <t>63.88 ± 16.24</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>88.28 ± 4.06</t>
+          <t>84.23 ± 7.43</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>83.01 ± 5.85</t>
+          <t>82.70 ± 9.03</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>47.45 ± 12.00</t>
+          <t>77.07 ± 20.87</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>11.82 ± 5.98</t>
+          <t>42.95 ± 30.52</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-0.42 ± 0.70</t>
+          <t>21.06 ± 28.45</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>16.75 ± 11.95</t>
+          <t>47.87 ± 26.97</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>57.36 ± 16.37</t>
+          <t>33.74 ± 28.02</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>8.33 ± 9.68</t>
+          <t>44.16 ± 37.85</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>4.26 ± 4.75</t>
+          <t>32.74 ± 37.70</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>11.53 ± 0.04</t>
+          <t>13.79 ± 0.05</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>88.47 ± 0.04</t>
+          <t>86.21 ± 0.05</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>11.76 ± 0.00</t>
+          <t>14.21 ± 0.01</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>88.24 ± 0.00</t>
+          <t>85.79 ± 0.01</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9302,72 +9302,72 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>54.00 ± 14.74</t>
+          <t>57.48 ± 11.98</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>85.82 ± 4.55</t>
+          <t>82.70 ± 6.11</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>82.01 ± 5.95</t>
+          <t>80.28 ± 7.62</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>45.72 ± 9.65</t>
+          <t>57.82 ± 13.20</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>11.29 ± 4.14</t>
+          <t>21.94 ± 11.22</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-2.15 ± 3.46</t>
+          <t>9.21 ± 15.34</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>15.49 ± 11.82</t>
+          <t>28.20 ± 12.78</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>57.24 ± 16.38</t>
+          <t>49.91 ± 19.15</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>5.19 ± 4.11</t>
+          <t>19.29 ± 14.80</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2.18 ± 2.12</t>
+          <t>14.25 ± 12.67</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>11.53 ± 0.04</t>
+          <t>13.79 ± 0.05</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>88.47 ± 0.04</t>
+          <t>86.21 ± 0.05</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>11.76 ± 0.00</t>
+          <t>14.21 ± 0.01</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>88.24 ± 0.00</t>
+          <t>85.79 ± 0.01</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9410,72 +9410,72 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>53.33 ± 12.17</t>
+          <t>59.34 ± 15.77</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>81.71 ± 4.51</t>
+          <t>79.06 ± 8.84</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>80.49 ± 5.13</t>
+          <t>78.88 ± 8.60</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>50.03 ± 5.59</t>
+          <t>55.38 ± 9.36</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>12.66 ± 4.63</t>
+          <t>19.57 ± 9.22</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-0.24 ± 8.85</t>
+          <t>9.31 ± 18.67</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>19.04 ± 12.25</t>
+          <t>31.01 ± 15.83</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>54.83 ± 15.38</t>
+          <t>50.44 ± 18.44</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>9.12 ± 8.41</t>
+          <t>12.34 ± 13.04</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>6.18 ± 5.66</t>
+          <t>8.69 ± 12.39</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>11.53 ± 0.04</t>
+          <t>13.79 ± 0.05</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>88.47 ± 0.04</t>
+          <t>86.21 ± 0.05</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>11.76 ± 0.00</t>
+          <t>14.21 ± 0.01</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>88.24 ± 0.00</t>
+          <t>85.79 ± 0.01</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9518,72 +9518,72 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>52.57 ± 13.60</t>
+          <t>55.38 ± 15.58</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>83.41 ± 4.70</t>
+          <t>79.06 ± 8.88</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>80.81 ± 5.54</t>
+          <t>78.04 ± 8.41</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>54.81 ± 20.20</t>
+          <t>69.89 ± 16.72</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>15.25 ± 7.78</t>
+          <t>28.76 ± 19.35</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-3.51 ± 6.18</t>
+          <t>2.80 ± 14.35</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>19.50 ± 12.33</t>
+          <t>33.78 ± 17.66</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>50.88 ± 21.89</t>
+          <t>38.39 ± 23.96</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>10.14 ± 10.69</t>
+          <t>24.15 ± 26.64</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>4.21 ± 4.94</t>
+          <t>14.11 ± 17.92</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>11.53 ± 0.04</t>
+          <t>13.79 ± 0.05</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>88.47 ± 0.04</t>
+          <t>86.21 ± 0.05</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>11.76 ± 0.00</t>
+          <t>14.21 ± 0.01</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>88.24 ± 0.00</t>
+          <t>85.79 ± 0.01</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
